--- a/output/pdf_financials_xlsx/UAV.X.xlsx
+++ b/output/pdf_financials_xlsx/UAV.X.xlsx
@@ -2195,16 +2195,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.969058</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.969058</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.969058</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.969058</v>
       </c>
     </row>
     <row r="93">
@@ -3744,7 +3744,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
         <v>2.969058</v>
       </c>

--- a/output/pdf_financials_xlsx/UAV.X.xlsx
+++ b/output/pdf_financials_xlsx/UAV.X.xlsx
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.000287</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.002562</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.141994</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.188522</v>
       </c>
     </row>
     <row r="35">
@@ -1115,16 +1115,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.000287</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.002562</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.141994</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.188522</v>
       </c>
     </row>
     <row r="37">
@@ -1343,16 +1343,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.000287</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.002562</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.141994</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.188522</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/UAV.X.xlsx
+++ b/output/pdf_financials_xlsx/UAV.X.xlsx
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="68">
